--- a/source/8、绩效异常岗位/5、封包岗/封包岗-6月.xlsx
+++ b/source/8、绩效异常岗位/5、封包岗/封包岗-6月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="75">
   <si>
     <t>数据日期</t>
   </si>
@@ -64,18 +64,12 @@
     <t>肃宁</t>
   </si>
   <si>
-    <t>76.8</t>
-  </si>
-  <si>
     <t>宁夏区</t>
   </si>
   <si>
     <t>银川</t>
   </si>
   <si>
-    <t>65.3</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -85,159 +79,102 @@
     <t>呼和浩特</t>
   </si>
   <si>
-    <t>74.5</t>
-  </si>
-  <si>
     <t>山西区</t>
   </si>
   <si>
     <t>太原</t>
   </si>
   <si>
-    <t>108.8</t>
-  </si>
-  <si>
     <t>湖南区</t>
   </si>
   <si>
     <t>衡阳</t>
   </si>
   <si>
-    <t>71.5</t>
-  </si>
-  <si>
     <t>石家庄</t>
   </si>
   <si>
-    <t>58.6</t>
-  </si>
-  <si>
     <t>邢邯</t>
   </si>
   <si>
-    <t>60.7</t>
-  </si>
-  <si>
     <t>贵州区</t>
   </si>
   <si>
     <t>贵阳</t>
   </si>
   <si>
-    <t>119.7</t>
-  </si>
-  <si>
     <t>湖北区</t>
   </si>
   <si>
     <t>武汉</t>
   </si>
   <si>
-    <t>89</t>
-  </si>
-  <si>
     <t>辽宁区</t>
   </si>
   <si>
     <t>盘锦</t>
   </si>
   <si>
-    <t>72.4</t>
-  </si>
-  <si>
     <t>沈阳</t>
   </si>
   <si>
-    <t>81.5</t>
-  </si>
-  <si>
     <t>黑龙江区</t>
   </si>
   <si>
     <t>哈尔滨</t>
   </si>
   <si>
-    <t>91.1</t>
-  </si>
-  <si>
     <t>山东区</t>
   </si>
   <si>
     <t>青岛</t>
   </si>
   <si>
-    <t>84.1</t>
-  </si>
-  <si>
     <t>河南区</t>
   </si>
   <si>
     <t>商丘</t>
   </si>
   <si>
-    <t>69.2</t>
-  </si>
-  <si>
     <t>浙北区</t>
   </si>
   <si>
     <t>东方天地港</t>
   </si>
   <si>
-    <t>97.3</t>
-  </si>
-  <si>
     <t>广西区</t>
   </si>
   <si>
     <t>柳州</t>
   </si>
   <si>
-    <t>65.2</t>
-  </si>
-  <si>
     <t>宁波</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>江西区</t>
   </si>
   <si>
     <t>横峰</t>
   </si>
   <si>
-    <t>57.6</t>
-  </si>
-  <si>
     <t>广东区</t>
   </si>
   <si>
     <t>深圳</t>
   </si>
   <si>
-    <t>98.9</t>
-  </si>
-  <si>
     <t>浙南区</t>
   </si>
   <si>
     <t>义乌</t>
   </si>
   <si>
-    <t>145.4</t>
-  </si>
-  <si>
     <t>江苏区</t>
   </si>
   <si>
     <t>南通</t>
   </si>
   <si>
-    <t>108.4</t>
-  </si>
-  <si>
     <t>陕西区</t>
   </si>
   <si>
@@ -250,37 +187,73 @@
     <t>长春</t>
   </si>
   <si>
-    <t>79.4</t>
-  </si>
-  <si>
     <t>南京</t>
   </si>
   <si>
-    <t>107.6</t>
-  </si>
-  <si>
     <t>长沙</t>
   </si>
   <si>
-    <t>107.5</t>
-  </si>
-  <si>
     <t>广州</t>
   </si>
   <si>
-    <t>112.2</t>
-  </si>
-  <si>
     <t>安徽区</t>
   </si>
   <si>
     <t>合肥</t>
   </si>
   <si>
-    <t>114.2</t>
-  </si>
-  <si>
     <t>佛山</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>长治</t>
+  </si>
+  <si>
+    <t>淮安</t>
+  </si>
+  <si>
+    <t>福建区</t>
+  </si>
+  <si>
+    <t>泉州</t>
+  </si>
+  <si>
+    <t>杭州</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>东莞</t>
+  </si>
+  <si>
+    <t>云南区</t>
+  </si>
+  <si>
+    <t>昆明</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>荆州</t>
+  </si>
+  <si>
+    <t>无锡</t>
+  </si>
+  <si>
+    <t>四川区</t>
+  </si>
+  <si>
+    <t>成都</t>
+  </si>
+  <si>
+    <t>常德</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1184,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1250,8 +1223,8 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
+      <c r="D2">
+        <v>76.8</v>
       </c>
       <c r="E2">
         <v>116.4</v>
@@ -1271,13 +1244,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
+      <c r="D3">
+        <v>65.3</v>
       </c>
       <c r="E3">
         <v>95.3</v>
@@ -1286,10 +1259,10 @@
         <v>45.8</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1297,13 +1270,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>74.5</v>
       </c>
       <c r="E4">
         <v>107.7</v>
@@ -1323,13 +1296,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>108.8</v>
       </c>
       <c r="E5">
         <v>154.6</v>
@@ -1349,13 +1322,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>71.5</v>
       </c>
       <c r="E6">
         <v>100.1</v>
@@ -1364,10 +1337,10 @@
         <v>39.9</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1378,10 +1351,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>58.6</v>
       </c>
       <c r="E7">
         <v>80</v>
@@ -1390,10 +1363,10 @@
         <v>36.5</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1404,10 +1377,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>60.7</v>
       </c>
       <c r="E8">
         <v>81.1</v>
@@ -1416,10 +1389,10 @@
         <v>33.5</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1427,13 +1400,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>119.7</v>
       </c>
       <c r="E9">
         <v>153.3</v>
@@ -1453,13 +1426,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>89</v>
       </c>
       <c r="E10">
         <v>109.8</v>
@@ -1479,13 +1452,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>72.4</v>
       </c>
       <c r="E11">
         <v>89.2</v>
@@ -1494,10 +1467,10 @@
         <v>23.1</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1505,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>81.5</v>
       </c>
       <c r="E12">
         <v>99.6</v>
@@ -1520,10 +1493,10 @@
         <v>22.2</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1531,13 +1504,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>91.1</v>
       </c>
       <c r="E13">
         <v>111.1</v>
@@ -1557,13 +1530,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
+        <v>32</v>
+      </c>
+      <c r="D14">
+        <v>84.1</v>
       </c>
       <c r="E14">
         <v>98.7</v>
@@ -1572,10 +1545,10 @@
         <v>17.2</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1583,13 +1556,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>48</v>
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>69.2</v>
       </c>
       <c r="E15">
         <v>81</v>
@@ -1598,10 +1571,10 @@
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1609,13 +1582,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
+        <v>36</v>
+      </c>
+      <c r="D16">
+        <v>97.3</v>
       </c>
       <c r="E16">
         <v>113.7</v>
@@ -1635,13 +1608,13 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>54</v>
+        <v>38</v>
+      </c>
+      <c r="D17">
+        <v>65.2</v>
       </c>
       <c r="E17">
         <v>75.5</v>
@@ -1650,10 +1623,10 @@
         <v>15.8</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1661,13 +1634,13 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
+        <v>39</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
       </c>
       <c r="E18">
         <v>114.5</v>
@@ -1687,13 +1660,13 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
+        <v>41</v>
+      </c>
+      <c r="D19">
+        <v>57.6</v>
       </c>
       <c r="E19">
         <v>66</v>
@@ -1702,10 +1675,10 @@
         <v>14.5</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1713,13 +1686,13 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>62</v>
+        <v>43</v>
+      </c>
+      <c r="D20">
+        <v>98.9</v>
       </c>
       <c r="E20">
         <v>112</v>
@@ -1739,13 +1712,13 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" t="s">
-        <v>65</v>
+        <v>45</v>
+      </c>
+      <c r="D21">
+        <v>145.4</v>
       </c>
       <c r="E21">
         <v>164.3</v>
@@ -1765,13 +1738,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>108.4</v>
       </c>
       <c r="E22">
         <v>122.4</v>
@@ -1791,13 +1764,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>56</v>
+        <v>49</v>
+      </c>
+      <c r="D23">
+        <v>100</v>
       </c>
       <c r="E23">
         <v>112.9</v>
@@ -1817,13 +1790,13 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" t="s">
-        <v>73</v>
+        <v>51</v>
+      </c>
+      <c r="D24">
+        <v>79.4</v>
       </c>
       <c r="E24">
         <v>88.6</v>
@@ -1832,10 +1805,10 @@
         <v>11.5</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1843,13 +1816,13 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>75</v>
+        <v>52</v>
+      </c>
+      <c r="D25">
+        <v>107.6</v>
       </c>
       <c r="E25">
         <v>117</v>
@@ -1869,13 +1842,13 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" t="s">
-        <v>77</v>
+        <v>53</v>
+      </c>
+      <c r="D26">
+        <v>107.5</v>
       </c>
       <c r="E26">
         <v>114.5</v>
@@ -1895,13 +1868,13 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" t="s">
-        <v>79</v>
+        <v>54</v>
+      </c>
+      <c r="D27">
+        <v>112.2</v>
       </c>
       <c r="E27">
         <v>119.1</v>
@@ -1921,13 +1894,13 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>82</v>
+        <v>56</v>
+      </c>
+      <c r="D28">
+        <v>114.2</v>
       </c>
       <c r="E28">
         <v>120.3</v>
@@ -1947,13 +1920,13 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="D29">
+        <v>107.6</v>
       </c>
       <c r="E29">
         <v>111.2</v>
@@ -1966,6 +1939,3438 @@
       </c>
       <c r="H29">
         <v>10.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30">
+        <v>60.7</v>
+      </c>
+      <c r="E30">
+        <v>81.8</v>
+      </c>
+      <c r="F30">
+        <v>34.7</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31">
+        <v>76.8</v>
+      </c>
+      <c r="E31">
+        <v>100.9</v>
+      </c>
+      <c r="F31">
+        <v>31.4</v>
+      </c>
+      <c r="G31">
+        <v>99.4</v>
+      </c>
+      <c r="H31">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32">
+        <v>65.3</v>
+      </c>
+      <c r="E32">
+        <v>85.4</v>
+      </c>
+      <c r="F32">
+        <v>30.7</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>58.6</v>
+      </c>
+      <c r="E33">
+        <v>75</v>
+      </c>
+      <c r="F33">
+        <v>28.1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34">
+        <v>74.5</v>
+      </c>
+      <c r="E34">
+        <v>94</v>
+      </c>
+      <c r="F34">
+        <v>26</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35">
+        <v>71.5</v>
+      </c>
+      <c r="E35">
+        <v>88.8</v>
+      </c>
+      <c r="F35">
+        <v>24.1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36">
+        <v>97.3</v>
+      </c>
+      <c r="E36">
+        <v>119.8</v>
+      </c>
+      <c r="F36">
+        <v>23.1</v>
+      </c>
+      <c r="G36">
+        <v>99.4</v>
+      </c>
+      <c r="H36">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37">
+        <v>110.7</v>
+      </c>
+      <c r="E37">
+        <v>132.9</v>
+      </c>
+      <c r="F37">
+        <v>20.1</v>
+      </c>
+      <c r="G37">
+        <v>99.4</v>
+      </c>
+      <c r="H37">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38">
+        <v>119.7</v>
+      </c>
+      <c r="E38">
+        <v>143.5</v>
+      </c>
+      <c r="F38">
+        <v>19.8</v>
+      </c>
+      <c r="G38">
+        <v>99.4</v>
+      </c>
+      <c r="H38">
+        <v>44.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39">
+        <v>84.2</v>
+      </c>
+      <c r="E39">
+        <v>100.1</v>
+      </c>
+      <c r="F39">
+        <v>18.8</v>
+      </c>
+      <c r="G39">
+        <v>99.4</v>
+      </c>
+      <c r="H39">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40">
+        <v>69.2</v>
+      </c>
+      <c r="E40">
+        <v>81.7</v>
+      </c>
+      <c r="F40">
+        <v>18.1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41">
+        <v>79</v>
+      </c>
+      <c r="E41">
+        <v>92.8</v>
+      </c>
+      <c r="F41">
+        <v>17.4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42">
+        <v>91.1</v>
+      </c>
+      <c r="E42">
+        <v>106.1</v>
+      </c>
+      <c r="F42">
+        <v>16.4</v>
+      </c>
+      <c r="G42">
+        <v>99.4</v>
+      </c>
+      <c r="H42">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43">
+        <v>100</v>
+      </c>
+      <c r="E43">
+        <v>115.9</v>
+      </c>
+      <c r="F43">
+        <v>15.9</v>
+      </c>
+      <c r="G43">
+        <v>99.4</v>
+      </c>
+      <c r="H43">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44">
+        <v>145.4</v>
+      </c>
+      <c r="E44">
+        <v>168.5</v>
+      </c>
+      <c r="F44">
+        <v>15.8</v>
+      </c>
+      <c r="G44">
+        <v>99.4</v>
+      </c>
+      <c r="H44">
+        <v>69.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45">
+        <v>100</v>
+      </c>
+      <c r="E45">
+        <v>114.5</v>
+      </c>
+      <c r="F45">
+        <v>14.5</v>
+      </c>
+      <c r="G45">
+        <v>99.4</v>
+      </c>
+      <c r="H45">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46">
+        <v>108.4</v>
+      </c>
+      <c r="E46">
+        <v>123.7</v>
+      </c>
+      <c r="F46">
+        <v>14.1</v>
+      </c>
+      <c r="G46">
+        <v>99.4</v>
+      </c>
+      <c r="H46">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47">
+        <v>98.9</v>
+      </c>
+      <c r="E47">
+        <v>112.9</v>
+      </c>
+      <c r="F47">
+        <v>14.1</v>
+      </c>
+      <c r="G47">
+        <v>99.4</v>
+      </c>
+      <c r="H47">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48">
+        <v>72.4</v>
+      </c>
+      <c r="E48">
+        <v>82.5</v>
+      </c>
+      <c r="F48">
+        <v>13.8</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49">
+        <v>104.5</v>
+      </c>
+      <c r="E49">
+        <v>118.1</v>
+      </c>
+      <c r="F49">
+        <v>13</v>
+      </c>
+      <c r="G49">
+        <v>99.4</v>
+      </c>
+      <c r="H49">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50">
+        <v>89</v>
+      </c>
+      <c r="E50">
+        <v>100.5</v>
+      </c>
+      <c r="F50">
+        <v>12.9</v>
+      </c>
+      <c r="G50">
+        <v>99.4</v>
+      </c>
+      <c r="H50">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51">
+        <v>81.5</v>
+      </c>
+      <c r="E51">
+        <v>90.6</v>
+      </c>
+      <c r="F51">
+        <v>11.2</v>
+      </c>
+      <c r="G51" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52">
+        <v>71.6</v>
+      </c>
+      <c r="E52">
+        <v>79.1</v>
+      </c>
+      <c r="F52">
+        <v>10.5</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53">
+        <v>77.9</v>
+      </c>
+      <c r="E53">
+        <v>85.8</v>
+      </c>
+      <c r="F53">
+        <v>10.1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54">
+        <v>112.2</v>
+      </c>
+      <c r="E54">
+        <v>121</v>
+      </c>
+      <c r="F54">
+        <v>7.8</v>
+      </c>
+      <c r="G54">
+        <v>99.4</v>
+      </c>
+      <c r="H54">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55">
+        <v>103.4</v>
+      </c>
+      <c r="E55">
+        <v>110.9</v>
+      </c>
+      <c r="F55">
+        <v>7.3</v>
+      </c>
+      <c r="G55">
+        <v>99.4</v>
+      </c>
+      <c r="H55">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56">
+        <v>114.2</v>
+      </c>
+      <c r="E56">
+        <v>121.9</v>
+      </c>
+      <c r="F56">
+        <v>6.8</v>
+      </c>
+      <c r="G56">
+        <v>99.4</v>
+      </c>
+      <c r="H56">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57">
+        <v>104.5</v>
+      </c>
+      <c r="E57">
+        <v>111.1</v>
+      </c>
+      <c r="F57">
+        <v>6.3</v>
+      </c>
+      <c r="G57">
+        <v>99.4</v>
+      </c>
+      <c r="H57">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58">
+        <v>108.7</v>
+      </c>
+      <c r="E58">
+        <v>114.9</v>
+      </c>
+      <c r="F58">
+        <v>5.6</v>
+      </c>
+      <c r="G58">
+        <v>99.4</v>
+      </c>
+      <c r="H58">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>42</v>
+      </c>
+      <c r="C59" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59">
+        <v>107.6</v>
+      </c>
+      <c r="E59">
+        <v>112.8</v>
+      </c>
+      <c r="F59">
+        <v>4.7</v>
+      </c>
+      <c r="G59">
+        <v>99.4</v>
+      </c>
+      <c r="H59">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60">
+        <v>76.8</v>
+      </c>
+      <c r="E60">
+        <v>98.9</v>
+      </c>
+      <c r="F60">
+        <v>28.8</v>
+      </c>
+      <c r="G60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61">
+        <v>60.7</v>
+      </c>
+      <c r="E61">
+        <v>78.2</v>
+      </c>
+      <c r="F61">
+        <v>28.7</v>
+      </c>
+      <c r="G61" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62">
+        <v>58.6</v>
+      </c>
+      <c r="E62">
+        <v>73.6</v>
+      </c>
+      <c r="F62">
+        <v>25.6</v>
+      </c>
+      <c r="G62" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63">
+        <v>65.3</v>
+      </c>
+      <c r="E63">
+        <v>81.4</v>
+      </c>
+      <c r="F63">
+        <v>24.5</v>
+      </c>
+      <c r="G63" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64">
+        <v>97.3</v>
+      </c>
+      <c r="E64">
+        <v>120.1</v>
+      </c>
+      <c r="F64">
+        <v>23.4</v>
+      </c>
+      <c r="G64">
+        <v>99.3</v>
+      </c>
+      <c r="H64">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65">
+        <v>74.5</v>
+      </c>
+      <c r="E65">
+        <v>91.7</v>
+      </c>
+      <c r="F65">
+        <v>22.9</v>
+      </c>
+      <c r="G65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66">
+        <v>69.2</v>
+      </c>
+      <c r="E66">
+        <v>83.8</v>
+      </c>
+      <c r="F66">
+        <v>21</v>
+      </c>
+      <c r="G66" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>64</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67">
+        <v>71.5</v>
+      </c>
+      <c r="E67">
+        <v>86.3</v>
+      </c>
+      <c r="F67">
+        <v>20.6</v>
+      </c>
+      <c r="G67" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" t="s">
+        <v>51</v>
+      </c>
+      <c r="D68">
+        <v>79</v>
+      </c>
+      <c r="E68">
+        <v>94.4</v>
+      </c>
+      <c r="F68">
+        <v>19.4</v>
+      </c>
+      <c r="G68" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69">
+        <v>119.7</v>
+      </c>
+      <c r="E69">
+        <v>140.9</v>
+      </c>
+      <c r="F69">
+        <v>17.7</v>
+      </c>
+      <c r="G69">
+        <v>99.3</v>
+      </c>
+      <c r="H69">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70">
+        <v>100</v>
+      </c>
+      <c r="E70">
+        <v>117.5</v>
+      </c>
+      <c r="F70">
+        <v>17.5</v>
+      </c>
+      <c r="G70">
+        <v>99.3</v>
+      </c>
+      <c r="H70">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71">
+        <v>84.2</v>
+      </c>
+      <c r="E71">
+        <v>98.4</v>
+      </c>
+      <c r="F71">
+        <v>16.9</v>
+      </c>
+      <c r="G71" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" t="s">
+        <v>44</v>
+      </c>
+      <c r="C72" t="s">
+        <v>45</v>
+      </c>
+      <c r="D72">
+        <v>145.4</v>
+      </c>
+      <c r="E72">
+        <v>169.9</v>
+      </c>
+      <c r="F72">
+        <v>16.8</v>
+      </c>
+      <c r="G72">
+        <v>99.3</v>
+      </c>
+      <c r="H72">
+        <v>70.9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>64</v>
+      </c>
+      <c r="B73" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73">
+        <v>91.1</v>
+      </c>
+      <c r="E73">
+        <v>106.5</v>
+      </c>
+      <c r="F73">
+        <v>16.8</v>
+      </c>
+      <c r="G73">
+        <v>99.3</v>
+      </c>
+      <c r="H73">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74">
+        <v>110.7</v>
+      </c>
+      <c r="E74">
+        <v>127.4</v>
+      </c>
+      <c r="F74">
+        <v>15.1</v>
+      </c>
+      <c r="G74">
+        <v>99.3</v>
+      </c>
+      <c r="H74">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" t="s">
+        <v>42</v>
+      </c>
+      <c r="C75" t="s">
+        <v>43</v>
+      </c>
+      <c r="D75">
+        <v>98.9</v>
+      </c>
+      <c r="E75">
+        <v>113.5</v>
+      </c>
+      <c r="F75">
+        <v>14.7</v>
+      </c>
+      <c r="G75">
+        <v>99.3</v>
+      </c>
+      <c r="H75">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" t="s">
+        <v>48</v>
+      </c>
+      <c r="C76" t="s">
+        <v>49</v>
+      </c>
+      <c r="D76">
+        <v>100</v>
+      </c>
+      <c r="E76">
+        <v>114.7</v>
+      </c>
+      <c r="F76">
+        <v>14.7</v>
+      </c>
+      <c r="G76">
+        <v>99.3</v>
+      </c>
+      <c r="H76">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="s">
+        <v>59</v>
+      </c>
+      <c r="D77">
+        <v>71.6</v>
+      </c>
+      <c r="E77">
+        <v>80.4</v>
+      </c>
+      <c r="F77">
+        <v>12.2</v>
+      </c>
+      <c r="G77" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78">
+        <v>89</v>
+      </c>
+      <c r="E78">
+        <v>99.3</v>
+      </c>
+      <c r="F78">
+        <v>11.6</v>
+      </c>
+      <c r="G78">
+        <v>99.3</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" t="s">
+        <v>47</v>
+      </c>
+      <c r="D79">
+        <v>108.4</v>
+      </c>
+      <c r="E79">
+        <v>120.4</v>
+      </c>
+      <c r="F79">
+        <v>11.1</v>
+      </c>
+      <c r="G79">
+        <v>99.3</v>
+      </c>
+      <c r="H79">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80" t="s">
+        <v>46</v>
+      </c>
+      <c r="C80" t="s">
+        <v>60</v>
+      </c>
+      <c r="D80">
+        <v>77.9</v>
+      </c>
+      <c r="E80">
+        <v>86.3</v>
+      </c>
+      <c r="F80">
+        <v>10.7</v>
+      </c>
+      <c r="G80" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>64</v>
+      </c>
+      <c r="B81" t="s">
+        <v>42</v>
+      </c>
+      <c r="C81" t="s">
+        <v>65</v>
+      </c>
+      <c r="D81">
+        <v>88.4</v>
+      </c>
+      <c r="E81">
+        <v>97.8</v>
+      </c>
+      <c r="F81">
+        <v>10.5</v>
+      </c>
+      <c r="G81" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>64</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D82">
+        <v>72.4</v>
+      </c>
+      <c r="E82">
+        <v>79.9</v>
+      </c>
+      <c r="F82">
+        <v>10.3</v>
+      </c>
+      <c r="G82" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>64</v>
+      </c>
+      <c r="B83" t="s">
+        <v>55</v>
+      </c>
+      <c r="C83" t="s">
+        <v>56</v>
+      </c>
+      <c r="D83">
+        <v>113.6</v>
+      </c>
+      <c r="E83">
+        <v>125.4</v>
+      </c>
+      <c r="F83">
+        <v>10.3</v>
+      </c>
+      <c r="G83">
+        <v>99.3</v>
+      </c>
+      <c r="H83">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>64</v>
+      </c>
+      <c r="B84" t="s">
+        <v>46</v>
+      </c>
+      <c r="C84" t="s">
+        <v>52</v>
+      </c>
+      <c r="D84">
+        <v>104.5</v>
+      </c>
+      <c r="E84">
+        <v>114.7</v>
+      </c>
+      <c r="F84">
+        <v>9.8</v>
+      </c>
+      <c r="G84">
+        <v>99.3</v>
+      </c>
+      <c r="H84">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>64</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" t="s">
+        <v>53</v>
+      </c>
+      <c r="D85">
+        <v>108.7</v>
+      </c>
+      <c r="E85">
+        <v>118.5</v>
+      </c>
+      <c r="F85">
+        <v>9</v>
+      </c>
+      <c r="G85">
+        <v>99.3</v>
+      </c>
+      <c r="H85">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>64</v>
+      </c>
+      <c r="B86" t="s">
+        <v>42</v>
+      </c>
+      <c r="C86" t="s">
+        <v>54</v>
+      </c>
+      <c r="D86">
+        <v>112.2</v>
+      </c>
+      <c r="E86">
+        <v>121.6</v>
+      </c>
+      <c r="F86">
+        <v>8.3</v>
+      </c>
+      <c r="G86">
+        <v>99.3</v>
+      </c>
+      <c r="H86">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>64</v>
+      </c>
+      <c r="B87" t="s">
+        <v>61</v>
+      </c>
+      <c r="C87" t="s">
+        <v>62</v>
+      </c>
+      <c r="D87">
+        <v>103.4</v>
+      </c>
+      <c r="E87">
+        <v>110.7</v>
+      </c>
+      <c r="F87">
+        <v>7</v>
+      </c>
+      <c r="G87">
+        <v>99.3</v>
+      </c>
+      <c r="H87">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>64</v>
+      </c>
+      <c r="B88" t="s">
+        <v>35</v>
+      </c>
+      <c r="C88" t="s">
+        <v>63</v>
+      </c>
+      <c r="D88">
+        <v>104.5</v>
+      </c>
+      <c r="E88">
+        <v>111.3</v>
+      </c>
+      <c r="F88">
+        <v>6.5</v>
+      </c>
+      <c r="G88">
+        <v>99.3</v>
+      </c>
+      <c r="H88">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>64</v>
+      </c>
+      <c r="B89" t="s">
+        <v>66</v>
+      </c>
+      <c r="C89" t="s">
+        <v>67</v>
+      </c>
+      <c r="D89">
+        <v>105.3</v>
+      </c>
+      <c r="E89">
+        <v>111.3</v>
+      </c>
+      <c r="F89">
+        <v>5.7</v>
+      </c>
+      <c r="G89">
+        <v>99.3</v>
+      </c>
+      <c r="H89">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>64</v>
+      </c>
+      <c r="B90" t="s">
+        <v>42</v>
+      </c>
+      <c r="C90" t="s">
+        <v>57</v>
+      </c>
+      <c r="D90">
+        <v>107.6</v>
+      </c>
+      <c r="E90">
+        <v>113.4</v>
+      </c>
+      <c r="F90">
+        <v>5.3</v>
+      </c>
+      <c r="G90">
+        <v>99.3</v>
+      </c>
+      <c r="H90">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>68</v>
+      </c>
+      <c r="B91" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91">
+        <v>60.7</v>
+      </c>
+      <c r="E91">
+        <v>77.4</v>
+      </c>
+      <c r="F91">
+        <v>27.4</v>
+      </c>
+      <c r="G91" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>68</v>
+      </c>
+      <c r="B92" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92">
+        <v>76.8</v>
+      </c>
+      <c r="E92">
+        <v>97.8</v>
+      </c>
+      <c r="F92">
+        <v>27.3</v>
+      </c>
+      <c r="G92" t="s">
+        <v>13</v>
+      </c>
+      <c r="H92" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" t="s">
+        <v>35</v>
+      </c>
+      <c r="C93" t="s">
+        <v>36</v>
+      </c>
+      <c r="D93">
+        <v>97.3</v>
+      </c>
+      <c r="E93">
+        <v>123.4</v>
+      </c>
+      <c r="F93">
+        <v>26.8</v>
+      </c>
+      <c r="G93">
+        <v>99.5</v>
+      </c>
+      <c r="H93">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>68</v>
+      </c>
+      <c r="B94" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" t="s">
+        <v>20</v>
+      </c>
+      <c r="D94">
+        <v>58.6</v>
+      </c>
+      <c r="E94">
+        <v>73.6</v>
+      </c>
+      <c r="F94">
+        <v>25.6</v>
+      </c>
+      <c r="G94" t="s">
+        <v>13</v>
+      </c>
+      <c r="H94" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>68</v>
+      </c>
+      <c r="B95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95">
+        <v>65.3</v>
+      </c>
+      <c r="E95">
+        <v>80.4</v>
+      </c>
+      <c r="F95">
+        <v>23.1</v>
+      </c>
+      <c r="G95" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>68</v>
+      </c>
+      <c r="B96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96">
+        <v>74.5</v>
+      </c>
+      <c r="E96">
+        <v>90.7</v>
+      </c>
+      <c r="F96">
+        <v>21.6</v>
+      </c>
+      <c r="G96" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>68</v>
+      </c>
+      <c r="B97" t="s">
+        <v>50</v>
+      </c>
+      <c r="C97" t="s">
+        <v>51</v>
+      </c>
+      <c r="D97">
+        <v>79</v>
+      </c>
+      <c r="E97">
+        <v>95.5</v>
+      </c>
+      <c r="F97">
+        <v>20.7</v>
+      </c>
+      <c r="G97" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>68</v>
+      </c>
+      <c r="B98" t="s">
+        <v>33</v>
+      </c>
+      <c r="C98" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98">
+        <v>69.2</v>
+      </c>
+      <c r="E98">
+        <v>83.1</v>
+      </c>
+      <c r="F98">
+        <v>20.1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99">
+        <v>71.6</v>
+      </c>
+      <c r="E99">
+        <v>85.5</v>
+      </c>
+      <c r="F99">
+        <v>19.4</v>
+      </c>
+      <c r="G99" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>68</v>
+      </c>
+      <c r="B100" t="s">
+        <v>35</v>
+      </c>
+      <c r="C100" t="s">
+        <v>39</v>
+      </c>
+      <c r="D100">
+        <v>100</v>
+      </c>
+      <c r="E100">
+        <v>117.1</v>
+      </c>
+      <c r="F100">
+        <v>17.1</v>
+      </c>
+      <c r="G100">
+        <v>99.5</v>
+      </c>
+      <c r="H100">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>68</v>
+      </c>
+      <c r="B101" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101">
+        <v>91.4</v>
+      </c>
+      <c r="E101">
+        <v>107</v>
+      </c>
+      <c r="F101">
+        <v>17</v>
+      </c>
+      <c r="G101">
+        <v>99.5</v>
+      </c>
+      <c r="H101">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>68</v>
+      </c>
+      <c r="B102" t="s">
+        <v>31</v>
+      </c>
+      <c r="C102" t="s">
+        <v>32</v>
+      </c>
+      <c r="D102">
+        <v>84.2</v>
+      </c>
+      <c r="E102">
+        <v>98.2</v>
+      </c>
+      <c r="F102">
+        <v>16.6</v>
+      </c>
+      <c r="G102" t="s">
+        <v>13</v>
+      </c>
+      <c r="H102" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>68</v>
+      </c>
+      <c r="B103" t="s">
+        <v>44</v>
+      </c>
+      <c r="C103" t="s">
+        <v>45</v>
+      </c>
+      <c r="D103">
+        <v>145.4</v>
+      </c>
+      <c r="E103">
+        <v>169.1</v>
+      </c>
+      <c r="F103">
+        <v>16.3</v>
+      </c>
+      <c r="G103">
+        <v>99.5</v>
+      </c>
+      <c r="H103">
+        <v>69.9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>68</v>
+      </c>
+      <c r="B104" t="s">
+        <v>42</v>
+      </c>
+      <c r="C104" t="s">
+        <v>43</v>
+      </c>
+      <c r="D104">
+        <v>98.9</v>
+      </c>
+      <c r="E104">
+        <v>114.1</v>
+      </c>
+      <c r="F104">
+        <v>15.4</v>
+      </c>
+      <c r="G104">
+        <v>99.5</v>
+      </c>
+      <c r="H104">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>68</v>
+      </c>
+      <c r="B105" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" t="s">
+        <v>49</v>
+      </c>
+      <c r="D105">
+        <v>100</v>
+      </c>
+      <c r="E105">
+        <v>115.4</v>
+      </c>
+      <c r="F105">
+        <v>15.4</v>
+      </c>
+      <c r="G105">
+        <v>99.5</v>
+      </c>
+      <c r="H105">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>68</v>
+      </c>
+      <c r="B106" t="s">
+        <v>22</v>
+      </c>
+      <c r="C106" t="s">
+        <v>23</v>
+      </c>
+      <c r="D106">
+        <v>119.7</v>
+      </c>
+      <c r="E106">
+        <v>137.5</v>
+      </c>
+      <c r="F106">
+        <v>14.8</v>
+      </c>
+      <c r="G106">
+        <v>99.5</v>
+      </c>
+      <c r="H106">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>68</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="s">
+        <v>59</v>
+      </c>
+      <c r="D107">
+        <v>71.6</v>
+      </c>
+      <c r="E107">
+        <v>81.2</v>
+      </c>
+      <c r="F107">
+        <v>13.4</v>
+      </c>
+      <c r="G107" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>68</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108">
+        <v>110.7</v>
+      </c>
+      <c r="E108">
+        <v>124.3</v>
+      </c>
+      <c r="F108">
+        <v>12.3</v>
+      </c>
+      <c r="G108">
+        <v>99.5</v>
+      </c>
+      <c r="H108">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>68</v>
+      </c>
+      <c r="B109" t="s">
+        <v>42</v>
+      </c>
+      <c r="C109" t="s">
+        <v>65</v>
+      </c>
+      <c r="D109">
+        <v>88.4</v>
+      </c>
+      <c r="E109">
+        <v>98.2</v>
+      </c>
+      <c r="F109">
+        <v>11.1</v>
+      </c>
+      <c r="G109" t="s">
+        <v>13</v>
+      </c>
+      <c r="H109" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>68</v>
+      </c>
+      <c r="B110" t="s">
+        <v>46</v>
+      </c>
+      <c r="C110" t="s">
+        <v>60</v>
+      </c>
+      <c r="D110">
+        <v>77.9</v>
+      </c>
+      <c r="E110">
+        <v>86.5</v>
+      </c>
+      <c r="F110">
+        <v>11</v>
+      </c>
+      <c r="G110" t="s">
+        <v>13</v>
+      </c>
+      <c r="H110" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>68</v>
+      </c>
+      <c r="B111" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" t="s">
+        <v>69</v>
+      </c>
+      <c r="D111">
+        <v>80.7</v>
+      </c>
+      <c r="E111">
+        <v>89.4</v>
+      </c>
+      <c r="F111">
+        <v>10.7</v>
+      </c>
+      <c r="G111" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>68</v>
+      </c>
+      <c r="B112" t="s">
+        <v>46</v>
+      </c>
+      <c r="C112" t="s">
+        <v>70</v>
+      </c>
+      <c r="D112">
+        <v>86.8</v>
+      </c>
+      <c r="E112">
+        <v>96</v>
+      </c>
+      <c r="F112">
+        <v>10.5</v>
+      </c>
+      <c r="G112" t="s">
+        <v>13</v>
+      </c>
+      <c r="H112" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>68</v>
+      </c>
+      <c r="B113" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" t="s">
+        <v>28</v>
+      </c>
+      <c r="D113">
+        <v>81.5</v>
+      </c>
+      <c r="E113">
+        <v>90.1</v>
+      </c>
+      <c r="F113">
+        <v>10.5</v>
+      </c>
+      <c r="G113" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>68</v>
+      </c>
+      <c r="B114" t="s">
+        <v>46</v>
+      </c>
+      <c r="C114" t="s">
+        <v>52</v>
+      </c>
+      <c r="D114">
+        <v>104.5</v>
+      </c>
+      <c r="E114">
+        <v>115.5</v>
+      </c>
+      <c r="F114">
+        <v>10.5</v>
+      </c>
+      <c r="G114">
+        <v>99.5</v>
+      </c>
+      <c r="H114">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>68</v>
+      </c>
+      <c r="B115" t="s">
+        <v>40</v>
+      </c>
+      <c r="C115" t="s">
+        <v>41</v>
+      </c>
+      <c r="D115">
+        <v>57.6</v>
+      </c>
+      <c r="E115">
+        <v>63.7</v>
+      </c>
+      <c r="F115">
+        <v>10.4</v>
+      </c>
+      <c r="G115" t="s">
+        <v>13</v>
+      </c>
+      <c r="H115" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>68</v>
+      </c>
+      <c r="B116" t="s">
+        <v>71</v>
+      </c>
+      <c r="C116" t="s">
+        <v>72</v>
+      </c>
+      <c r="D116">
+        <v>93</v>
+      </c>
+      <c r="E116">
+        <v>102.6</v>
+      </c>
+      <c r="F116">
+        <v>10.3</v>
+      </c>
+      <c r="G116">
+        <v>99.5</v>
+      </c>
+      <c r="H116">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>68</v>
+      </c>
+      <c r="B117" t="s">
+        <v>46</v>
+      </c>
+      <c r="C117" t="s">
+        <v>47</v>
+      </c>
+      <c r="D117">
+        <v>108.4</v>
+      </c>
+      <c r="E117">
+        <v>119.5</v>
+      </c>
+      <c r="F117">
+        <v>10.2</v>
+      </c>
+      <c r="G117">
+        <v>99.5</v>
+      </c>
+      <c r="H117">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>68</v>
+      </c>
+      <c r="B118" t="s">
+        <v>18</v>
+      </c>
+      <c r="C118" t="s">
+        <v>73</v>
+      </c>
+      <c r="D118">
+        <v>75.3</v>
+      </c>
+      <c r="E118">
+        <v>83</v>
+      </c>
+      <c r="F118">
+        <v>10.1</v>
+      </c>
+      <c r="G118" t="s">
+        <v>13</v>
+      </c>
+      <c r="H118" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>68</v>
+      </c>
+      <c r="B119" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" t="s">
+        <v>25</v>
+      </c>
+      <c r="D119">
+        <v>89</v>
+      </c>
+      <c r="E119">
+        <v>97.9</v>
+      </c>
+      <c r="F119">
+        <v>10</v>
+      </c>
+      <c r="G119" t="s">
+        <v>13</v>
+      </c>
+      <c r="H119" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>68</v>
+      </c>
+      <c r="B120" t="s">
+        <v>55</v>
+      </c>
+      <c r="C120" t="s">
+        <v>56</v>
+      </c>
+      <c r="D120">
+        <v>113.6</v>
+      </c>
+      <c r="E120">
+        <v>124.2</v>
+      </c>
+      <c r="F120">
+        <v>9.3</v>
+      </c>
+      <c r="G120">
+        <v>99.5</v>
+      </c>
+      <c r="H120">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>68</v>
+      </c>
+      <c r="B121" t="s">
+        <v>42</v>
+      </c>
+      <c r="C121" t="s">
+        <v>54</v>
+      </c>
+      <c r="D121">
+        <v>112.2</v>
+      </c>
+      <c r="E121">
+        <v>122.6</v>
+      </c>
+      <c r="F121">
+        <v>9.2</v>
+      </c>
+      <c r="G121">
+        <v>99.5</v>
+      </c>
+      <c r="H121">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>68</v>
+      </c>
+      <c r="B122" t="s">
+        <v>18</v>
+      </c>
+      <c r="C122" t="s">
+        <v>53</v>
+      </c>
+      <c r="D122">
+        <v>108.7</v>
+      </c>
+      <c r="E122">
+        <v>117.5</v>
+      </c>
+      <c r="F122">
+        <v>8</v>
+      </c>
+      <c r="G122">
+        <v>99.5</v>
+      </c>
+      <c r="H122">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>68</v>
+      </c>
+      <c r="B123" t="s">
+        <v>35</v>
+      </c>
+      <c r="C123" t="s">
+        <v>63</v>
+      </c>
+      <c r="D123">
+        <v>104.5</v>
+      </c>
+      <c r="E123">
+        <v>112.2</v>
+      </c>
+      <c r="F123">
+        <v>7.4</v>
+      </c>
+      <c r="G123">
+        <v>99.5</v>
+      </c>
+      <c r="H123">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>68</v>
+      </c>
+      <c r="B124" t="s">
+        <v>61</v>
+      </c>
+      <c r="C124" t="s">
+        <v>62</v>
+      </c>
+      <c r="D124">
+        <v>103.4</v>
+      </c>
+      <c r="E124">
+        <v>110.8</v>
+      </c>
+      <c r="F124">
+        <v>7.1</v>
+      </c>
+      <c r="G124">
+        <v>99.5</v>
+      </c>
+      <c r="H124">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>68</v>
+      </c>
+      <c r="B125" t="s">
+        <v>42</v>
+      </c>
+      <c r="C125" t="s">
+        <v>57</v>
+      </c>
+      <c r="D125">
+        <v>107.6</v>
+      </c>
+      <c r="E125">
+        <v>115</v>
+      </c>
+      <c r="F125">
+        <v>6.8</v>
+      </c>
+      <c r="G125">
+        <v>99.5</v>
+      </c>
+      <c r="H125">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>68</v>
+      </c>
+      <c r="B126" t="s">
+        <v>66</v>
+      </c>
+      <c r="C126" t="s">
+        <v>67</v>
+      </c>
+      <c r="D126">
+        <v>105.3</v>
+      </c>
+      <c r="E126">
+        <v>111.4</v>
+      </c>
+      <c r="F126">
+        <v>5.8</v>
+      </c>
+      <c r="G126">
+        <v>99.5</v>
+      </c>
+      <c r="H126">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>74</v>
+      </c>
+      <c r="B127" t="s">
+        <v>35</v>
+      </c>
+      <c r="C127" t="s">
+        <v>36</v>
+      </c>
+      <c r="D127">
+        <v>97.3</v>
+      </c>
+      <c r="E127">
+        <v>123</v>
+      </c>
+      <c r="F127">
+        <v>26.5</v>
+      </c>
+      <c r="G127">
+        <v>99.3</v>
+      </c>
+      <c r="H127">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>74</v>
+      </c>
+      <c r="B128" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128">
+        <v>76.8</v>
+      </c>
+      <c r="E128">
+        <v>96.7</v>
+      </c>
+      <c r="F128">
+        <v>25.9</v>
+      </c>
+      <c r="G128" t="s">
+        <v>13</v>
+      </c>
+      <c r="H128" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>74</v>
+      </c>
+      <c r="B129" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129">
+        <v>60.7</v>
+      </c>
+      <c r="E129">
+        <v>75.8</v>
+      </c>
+      <c r="F129">
+        <v>24.7</v>
+      </c>
+      <c r="G129" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>74</v>
+      </c>
+      <c r="B130" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" t="s">
+        <v>20</v>
+      </c>
+      <c r="D130">
+        <v>58.6</v>
+      </c>
+      <c r="E130">
+        <v>73.1</v>
+      </c>
+      <c r="F130">
+        <v>24.7</v>
+      </c>
+      <c r="G130" t="s">
+        <v>13</v>
+      </c>
+      <c r="H130" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>74</v>
+      </c>
+      <c r="B131" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131">
+        <v>65.3</v>
+      </c>
+      <c r="E131">
+        <v>81.3</v>
+      </c>
+      <c r="F131">
+        <v>24.4</v>
+      </c>
+      <c r="G131" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>74</v>
+      </c>
+      <c r="B132" t="s">
+        <v>33</v>
+      </c>
+      <c r="C132" t="s">
+        <v>34</v>
+      </c>
+      <c r="D132">
+        <v>69.2</v>
+      </c>
+      <c r="E132">
+        <v>85.1</v>
+      </c>
+      <c r="F132">
+        <v>22.9</v>
+      </c>
+      <c r="G132" t="s">
+        <v>13</v>
+      </c>
+      <c r="H132" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>74</v>
+      </c>
+      <c r="B133" t="s">
+        <v>14</v>
+      </c>
+      <c r="C133" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133">
+        <v>74.5</v>
+      </c>
+      <c r="E133">
+        <v>90.1</v>
+      </c>
+      <c r="F133">
+        <v>20.8</v>
+      </c>
+      <c r="G133" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>74</v>
+      </c>
+      <c r="B134" t="s">
+        <v>50</v>
+      </c>
+      <c r="C134" t="s">
+        <v>51</v>
+      </c>
+      <c r="D134">
+        <v>79</v>
+      </c>
+      <c r="E134">
+        <v>95.5</v>
+      </c>
+      <c r="F134">
+        <v>20.7</v>
+      </c>
+      <c r="G134" t="s">
+        <v>13</v>
+      </c>
+      <c r="H134" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>74</v>
+      </c>
+      <c r="B135" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135">
+        <v>71.6</v>
+      </c>
+      <c r="E135">
+        <v>85</v>
+      </c>
+      <c r="F135">
+        <v>18.7</v>
+      </c>
+      <c r="G135" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>74</v>
+      </c>
+      <c r="B136" t="s">
+        <v>35</v>
+      </c>
+      <c r="C136" t="s">
+        <v>39</v>
+      </c>
+      <c r="D136">
+        <v>100</v>
+      </c>
+      <c r="E136">
+        <v>118.3</v>
+      </c>
+      <c r="F136">
+        <v>18.3</v>
+      </c>
+      <c r="G136">
+        <v>99.3</v>
+      </c>
+      <c r="H136">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>74</v>
+      </c>
+      <c r="B137" t="s">
+        <v>29</v>
+      </c>
+      <c r="C137" t="s">
+        <v>30</v>
+      </c>
+      <c r="D137">
+        <v>91.4</v>
+      </c>
+      <c r="E137">
+        <v>106.8</v>
+      </c>
+      <c r="F137">
+        <v>16.8</v>
+      </c>
+      <c r="G137">
+        <v>99.3</v>
+      </c>
+      <c r="H137">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>74</v>
+      </c>
+      <c r="B138" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" t="s">
+        <v>32</v>
+      </c>
+      <c r="D138">
+        <v>84.2</v>
+      </c>
+      <c r="E138">
+        <v>98.2</v>
+      </c>
+      <c r="F138">
+        <v>16.7</v>
+      </c>
+      <c r="G138" t="s">
+        <v>13</v>
+      </c>
+      <c r="H138" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>74</v>
+      </c>
+      <c r="B139" t="s">
+        <v>44</v>
+      </c>
+      <c r="C139" t="s">
+        <v>45</v>
+      </c>
+      <c r="D139">
+        <v>145.4</v>
+      </c>
+      <c r="E139">
+        <v>169.5</v>
+      </c>
+      <c r="F139">
+        <v>16.5</v>
+      </c>
+      <c r="G139">
+        <v>99.3</v>
+      </c>
+      <c r="H139">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>74</v>
+      </c>
+      <c r="B140" t="s">
+        <v>48</v>
+      </c>
+      <c r="C140" t="s">
+        <v>49</v>
+      </c>
+      <c r="D140">
+        <v>100</v>
+      </c>
+      <c r="E140">
+        <v>116.1</v>
+      </c>
+      <c r="F140">
+        <v>16.1</v>
+      </c>
+      <c r="G140">
+        <v>99.3</v>
+      </c>
+      <c r="H140">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>74</v>
+      </c>
+      <c r="B141" t="s">
+        <v>42</v>
+      </c>
+      <c r="C141" t="s">
+        <v>43</v>
+      </c>
+      <c r="D141">
+        <v>98.9</v>
+      </c>
+      <c r="E141">
+        <v>114.8</v>
+      </c>
+      <c r="F141">
+        <v>16</v>
+      </c>
+      <c r="G141">
+        <v>99.3</v>
+      </c>
+      <c r="H141">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>74</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="s">
+        <v>59</v>
+      </c>
+      <c r="D142">
+        <v>71.6</v>
+      </c>
+      <c r="E142">
+        <v>82.3</v>
+      </c>
+      <c r="F142">
+        <v>15</v>
+      </c>
+      <c r="G142" t="s">
+        <v>13</v>
+      </c>
+      <c r="H142" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
+        <v>74</v>
+      </c>
+      <c r="B143" t="s">
+        <v>71</v>
+      </c>
+      <c r="C143" t="s">
+        <v>72</v>
+      </c>
+      <c r="D143">
+        <v>93</v>
+      </c>
+      <c r="E143">
+        <v>105.2</v>
+      </c>
+      <c r="F143">
+        <v>13</v>
+      </c>
+      <c r="G143">
+        <v>99.3</v>
+      </c>
+      <c r="H143">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
+        <v>74</v>
+      </c>
+      <c r="B144" t="s">
+        <v>22</v>
+      </c>
+      <c r="C144" t="s">
+        <v>23</v>
+      </c>
+      <c r="D144">
+        <v>119.7</v>
+      </c>
+      <c r="E144">
+        <v>134.7</v>
+      </c>
+      <c r="F144">
+        <v>12.4</v>
+      </c>
+      <c r="G144">
+        <v>99.3</v>
+      </c>
+      <c r="H144">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
+        <v>74</v>
+      </c>
+      <c r="B145" t="s">
+        <v>42</v>
+      </c>
+      <c r="C145" t="s">
+        <v>65</v>
+      </c>
+      <c r="D145">
+        <v>88.4</v>
+      </c>
+      <c r="E145">
+        <v>99.2</v>
+      </c>
+      <c r="F145">
+        <v>12.2</v>
+      </c>
+      <c r="G145">
+        <v>99.3</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>74</v>
+      </c>
+      <c r="B146" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" t="s">
+        <v>69</v>
+      </c>
+      <c r="D146">
+        <v>80.7</v>
+      </c>
+      <c r="E146">
+        <v>90</v>
+      </c>
+      <c r="F146">
+        <v>11.4</v>
+      </c>
+      <c r="G146" t="s">
+        <v>13</v>
+      </c>
+      <c r="H146" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>74</v>
+      </c>
+      <c r="B147" t="s">
+        <v>46</v>
+      </c>
+      <c r="C147" t="s">
+        <v>70</v>
+      </c>
+      <c r="D147">
+        <v>86.8</v>
+      </c>
+      <c r="E147">
+        <v>96.5</v>
+      </c>
+      <c r="F147">
+        <v>11.1</v>
+      </c>
+      <c r="G147" t="s">
+        <v>13</v>
+      </c>
+      <c r="H147" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>74</v>
+      </c>
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" t="s">
+        <v>28</v>
+      </c>
+      <c r="D148">
+        <v>81.5</v>
+      </c>
+      <c r="E148">
+        <v>90.4</v>
+      </c>
+      <c r="F148">
+        <v>10.9</v>
+      </c>
+      <c r="G148" t="s">
+        <v>13</v>
+      </c>
+      <c r="H148" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>74</v>
+      </c>
+      <c r="B149" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" t="s">
+        <v>27</v>
+      </c>
+      <c r="D149">
+        <v>72.4</v>
+      </c>
+      <c r="E149">
+        <v>79.8</v>
+      </c>
+      <c r="F149">
+        <v>10.2</v>
+      </c>
+      <c r="G149" t="s">
+        <v>13</v>
+      </c>
+      <c r="H149" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>74</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150">
+        <v>110.7</v>
+      </c>
+      <c r="E150">
+        <v>121.9</v>
+      </c>
+      <c r="F150">
+        <v>10.1</v>
+      </c>
+      <c r="G150">
+        <v>99.3</v>
+      </c>
+      <c r="H150">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>74</v>
+      </c>
+      <c r="B151" t="s">
+        <v>46</v>
+      </c>
+      <c r="C151" t="s">
+        <v>60</v>
+      </c>
+      <c r="D151">
+        <v>77.9</v>
+      </c>
+      <c r="E151">
+        <v>85.8</v>
+      </c>
+      <c r="F151">
+        <v>10.1</v>
+      </c>
+      <c r="G151" t="s">
+        <v>13</v>
+      </c>
+      <c r="H151" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>74</v>
+      </c>
+      <c r="B152" t="s">
+        <v>46</v>
+      </c>
+      <c r="C152" t="s">
+        <v>52</v>
+      </c>
+      <c r="D152">
+        <v>104.5</v>
+      </c>
+      <c r="E152">
+        <v>115</v>
+      </c>
+      <c r="F152">
+        <v>10</v>
+      </c>
+      <c r="G152">
+        <v>99.3</v>
+      </c>
+      <c r="H152">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>74</v>
+      </c>
+      <c r="B153" t="s">
+        <v>18</v>
+      </c>
+      <c r="C153" t="s">
+        <v>73</v>
+      </c>
+      <c r="D153">
+        <v>75.3</v>
+      </c>
+      <c r="E153">
+        <v>82.9</v>
+      </c>
+      <c r="F153">
+        <v>10</v>
+      </c>
+      <c r="G153" t="s">
+        <v>13</v>
+      </c>
+      <c r="H153" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>74</v>
+      </c>
+      <c r="B154" t="s">
+        <v>55</v>
+      </c>
+      <c r="C154" t="s">
+        <v>56</v>
+      </c>
+      <c r="D154">
+        <v>113.6</v>
+      </c>
+      <c r="E154">
+        <v>124.6</v>
+      </c>
+      <c r="F154">
+        <v>9.6</v>
+      </c>
+      <c r="G154">
+        <v>99.3</v>
+      </c>
+      <c r="H154">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>74</v>
+      </c>
+      <c r="B155" t="s">
+        <v>18</v>
+      </c>
+      <c r="C155" t="s">
+        <v>53</v>
+      </c>
+      <c r="D155">
+        <v>108.7</v>
+      </c>
+      <c r="E155">
+        <v>118.7</v>
+      </c>
+      <c r="F155">
+        <v>9.2</v>
+      </c>
+      <c r="G155">
+        <v>99.3</v>
+      </c>
+      <c r="H155">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>74</v>
+      </c>
+      <c r="B156" t="s">
+        <v>46</v>
+      </c>
+      <c r="C156" t="s">
+        <v>47</v>
+      </c>
+      <c r="D156">
+        <v>108.4</v>
+      </c>
+      <c r="E156">
+        <v>117.9</v>
+      </c>
+      <c r="F156">
+        <v>8.7</v>
+      </c>
+      <c r="G156">
+        <v>99.3</v>
+      </c>
+      <c r="H156">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" t="s">
+        <v>74</v>
+      </c>
+      <c r="B157" t="s">
+        <v>61</v>
+      </c>
+      <c r="C157" t="s">
+        <v>62</v>
+      </c>
+      <c r="D157">
+        <v>103.4</v>
+      </c>
+      <c r="E157">
+        <v>111.8</v>
+      </c>
+      <c r="F157">
+        <v>8.1</v>
+      </c>
+      <c r="G157">
+        <v>99.3</v>
+      </c>
+      <c r="H157">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" t="s">
+        <v>74</v>
+      </c>
+      <c r="B158" t="s">
+        <v>42</v>
+      </c>
+      <c r="C158" t="s">
+        <v>54</v>
+      </c>
+      <c r="D158">
+        <v>112.2</v>
+      </c>
+      <c r="E158">
+        <v>121</v>
+      </c>
+      <c r="F158">
+        <v>7.8</v>
+      </c>
+      <c r="G158">
+        <v>99.3</v>
+      </c>
+      <c r="H158">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" t="s">
+        <v>74</v>
+      </c>
+      <c r="B159" t="s">
+        <v>42</v>
+      </c>
+      <c r="C159" t="s">
+        <v>57</v>
+      </c>
+      <c r="D159">
+        <v>107.6</v>
+      </c>
+      <c r="E159">
+        <v>115.1</v>
+      </c>
+      <c r="F159">
+        <v>6.9</v>
+      </c>
+      <c r="G159">
+        <v>99.3</v>
+      </c>
+      <c r="H159">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" t="s">
+        <v>74</v>
+      </c>
+      <c r="B160" t="s">
+        <v>35</v>
+      </c>
+      <c r="C160" t="s">
+        <v>63</v>
+      </c>
+      <c r="D160">
+        <v>104.5</v>
+      </c>
+      <c r="E160">
+        <v>111.5</v>
+      </c>
+      <c r="F160">
+        <v>6.6</v>
+      </c>
+      <c r="G160">
+        <v>99.3</v>
+      </c>
+      <c r="H160">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" t="s">
+        <v>74</v>
+      </c>
+      <c r="B161" t="s">
+        <v>66</v>
+      </c>
+      <c r="C161" t="s">
+        <v>67</v>
+      </c>
+      <c r="D161">
+        <v>105.3</v>
+      </c>
+      <c r="E161">
+        <v>111.5</v>
+      </c>
+      <c r="F161">
+        <v>5.9</v>
+      </c>
+      <c r="G161">
+        <v>99.3</v>
+      </c>
+      <c r="H161">
+        <v>12.2</v>
       </c>
     </row>
   </sheetData>

--- a/source/8、绩效异常岗位/5、封包岗/封包岗-6月.xlsx
+++ b/source/8、绩效异常岗位/5、封包岗/封包岗-6月.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I571"/>
+  <dimension ref="A1:I721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22385,6 +22385,5748 @@
         <v>11.1</v>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>邢邯</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>50</v>
+      </c>
+      <c r="F572" t="n">
+        <v>74</v>
+      </c>
+      <c r="G572" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F573" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="G573" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F574" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G574" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F575" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G575" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F576" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="G576" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H576" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I576" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F577" t="n">
+        <v>89</v>
+      </c>
+      <c r="G577" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="F578" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="G578" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>吉林区</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F579" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="G579" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F580" t="n">
+        <v>79</v>
+      </c>
+      <c r="G580" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="F581" t="n">
+        <v>163.1</v>
+      </c>
+      <c r="G581" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H581" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I581" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F582" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="G582" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H582" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I582" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F583" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="G583" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H583" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I583" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F584" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="G584" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H584" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I584" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="F585" t="n">
+        <v>130.1</v>
+      </c>
+      <c r="G585" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H585" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I585" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="F586" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="G586" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H586" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I586" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F587" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="G587" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H587" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I587" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F588" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="G588" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H588" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I588" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F589" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="G589" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H589" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I589" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="F590" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="G590" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H590" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I590" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="F591" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="G591" t="n">
+        <v>3</v>
+      </c>
+      <c r="H591" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I591" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F592" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="G592" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H592" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I592" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="F593" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="G593" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H593" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I593" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="F594" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="G594" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="H594" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I594" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="F595" t="n">
+        <v>113</v>
+      </c>
+      <c r="G595" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="H595" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I595" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="F596" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="G596" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H596" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I596" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F597" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G597" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F598" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="G598" t="n">
+        <v>21</v>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="F599" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="G599" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F600" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="G600" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F601" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="G601" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H601" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I601" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F602" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="G602" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>吉林区</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F603" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G603" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="F604" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="G604" t="n">
+        <v>12</v>
+      </c>
+      <c r="H604" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I604" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F605" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G605" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F606" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="G606" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H606" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I606" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F607" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="G607" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H607" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I607" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>邢邯</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F608" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="G608" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F609" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="G609" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H609" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I609" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="F610" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="G610" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H610" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I610" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="F611" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="G611" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H611" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I611" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F612" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G612" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H612" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I612" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F613" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="G613" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H613" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I613" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F614" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="G614" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H614" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I614" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="F615" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="G615" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H615" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I615" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="F616" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G616" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H616" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I616" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="F617" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="G617" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H617" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I617" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F618" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="G618" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H618" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I618" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E619" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="F619" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="G619" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="H619" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I619" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E620" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="F620" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="G620" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="H620" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I620" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="F621" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="G621" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H621" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I621" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F622" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="G622" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F623" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G623" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="F624" t="n">
+        <v>88</v>
+      </c>
+      <c r="G624" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F625" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="G625" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F626" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="G626" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H626" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I626" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F627" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="G627" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>吉林区</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F628" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G628" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="F629" t="n">
+        <v>163</v>
+      </c>
+      <c r="G629" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H629" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I629" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E630" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F630" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="G630" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E631" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F631" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="G631" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H631" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I631" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>邢邯</t>
+        </is>
+      </c>
+      <c r="E632" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F632" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="G632" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E633" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F633" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="G633" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H633" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I633" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E634" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F634" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="G634" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H634" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I634" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E635" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="F635" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="G635" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H635" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I635" t="n">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E636" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="F636" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="G636" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H636" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I636" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E637" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F637" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="G637" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H637" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I637" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E638" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F638" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="G638" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H638" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I638" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E639" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="F639" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="G639" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H639" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I639" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E640" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F640" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="G640" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H640" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I640" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="F641" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G641" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H641" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I641" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E642" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="F642" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="G642" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H642" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I642" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F643" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="G643" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H643" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I643" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="F644" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="G644" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H644" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I644" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="F645" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="G645" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="H645" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I645" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="F646" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="G646" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="H646" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I646" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F647" t="n">
+        <v>76</v>
+      </c>
+      <c r="G647" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F648" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="G648" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F649" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="G649" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="F650" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="G650" t="n">
+        <v>19</v>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F651" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="G651" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H651" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I651" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F652" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="G652" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="F653" t="n">
+        <v>162.7</v>
+      </c>
+      <c r="G653" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H653" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I653" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>吉林区</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F654" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G654" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F655" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="G655" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F656" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="G656" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H656" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I656" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="F657" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="G657" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F658" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="G658" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H658" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I658" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F659" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="G659" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H659" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I659" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="F660" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="G660" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H660" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I660" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="F661" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="G661" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H661" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I661" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F662" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G662" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H662" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I662" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="F663" t="n">
+        <v>107</v>
+      </c>
+      <c r="G663" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H663" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I663" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F664" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="G664" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H664" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I664" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F665" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="G665" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H665" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I665" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="F666" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="G666" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H666" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I666" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="F667" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="G667" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H667" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I667" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F668" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="G668" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H668" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I668" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="F669" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="G669" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H669" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I669" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="F670" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="G670" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H670" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I670" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="F671" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="G671" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="H671" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I671" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F672" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="G672" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F673" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="G673" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="F674" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="G674" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F675" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="G675" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F676" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="G676" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H676" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I676" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F677" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="G677" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F678" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="G678" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="F679" t="n">
+        <v>162.7</v>
+      </c>
+      <c r="G679" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H679" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I679" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>吉林区</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F680" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G680" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="F681" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="G681" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F682" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="G682" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H682" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I682" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F683" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="G683" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H683" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I683" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F684" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="G684" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H684" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I684" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="F685" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="G685" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H685" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I685" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="F686" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="G686" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H686" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I686" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F687" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G687" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H687" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I687" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="F688" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="G688" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H688" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I688" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F689" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G689" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H689" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I689" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F690" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="G690" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H690" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I690" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="F691" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="G691" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H691" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I691" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="F692" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="G692" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H692" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I692" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F693" t="n">
+        <v>110</v>
+      </c>
+      <c r="G693" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H693" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I693" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="F694" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="G694" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H694" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I694" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="F695" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="G695" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="H695" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I695" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="F696" t="n">
+        <v>106</v>
+      </c>
+      <c r="G696" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H696" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I696" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="F697" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="G697" t="n">
+        <v>23</v>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>肃宁</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F698" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="G698" t="n">
+        <v>21</v>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>河北区</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F699" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="G699" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>辽宁区</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="F700" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="G700" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F701" t="n">
+        <v>121</v>
+      </c>
+      <c r="G701" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H701" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I701" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F702" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="G702" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F703" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="G703" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="F704" t="n">
+        <v>162.4</v>
+      </c>
+      <c r="G704" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H704" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I704" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>吉林区</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F705" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G705" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="F706" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="G706" t="n">
+        <v>11</v>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F707" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="G707" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H707" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I707" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F708" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="G708" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H708" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I708" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F709" t="n">
+        <v>112</v>
+      </c>
+      <c r="G709" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H709" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I709" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="F710" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="G710" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H710" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I710" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="F711" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="G711" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H711" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I711" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F712" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="G712" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H712" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I712" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="F713" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="G713" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H713" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I713" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F714" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="G714" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H714" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I714" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="F715" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="G715" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H715" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I715" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F716" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="G716" t="n">
+        <v>3</v>
+      </c>
+      <c r="H716" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I716" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="F717" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="G717" t="n">
+        <v>3</v>
+      </c>
+      <c r="H717" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I717" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F718" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="G718" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H718" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I718" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="F719" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="G719" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H719" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I719" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="F720" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="G720" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="H720" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I720" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>封包岗</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="F721" t="n">
+        <v>106</v>
+      </c>
+      <c r="G721" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H721" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I721" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
